--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488270_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488270_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8683</v>
+        <v>7.1671</v>
       </c>
       <c r="E2" t="n">
-        <v>3.216</v>
+        <v>1.6449</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6523</v>
+        <v>5.5222</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0778</v>
+        <v>3.6738</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5892</v>
+        <v>1.7386</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4886</v>
+        <v>1.9352</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6176</v>
+        <v>1.2679</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4518</v>
+        <v>0.5925</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1659</v>
+        <v>0.6755</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4602</v>
+        <v>2.4059</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1374</v>
+        <v>1.1462</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3227</v>
+        <v>1.2597</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1853</v>
+        <v>1.297</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0382</v>
+        <v>3.1499</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2913</v>
+        <v>-0.3215</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5084</v>
+        <v>-0.2879</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7829</v>
+        <v>-0.0336</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3139</v>
+        <v>2.5177</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9428</v>
+        <v>2.5177</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3415</v>
+        <v>5.3041</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8932</v>
+        <v>2.1935</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4483</v>
+        <v>3.1107</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6738</v>
+        <v>4.0778</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7386</v>
+        <v>3.5892</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9352</v>
+        <v>0.4886</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2679</v>
+        <v>2.6176</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5925</v>
+        <v>2.4518</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6755</v>
+        <v>0.1659</v>
       </c>
       <c r="M3" t="n">
-        <v>2.4059</v>
+        <v>1.4602</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1462</v>
+        <v>1.1374</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2597</v>
+        <v>0.3227</v>
       </c>
       <c r="P3" t="n">
-        <v>1.297</v>
+        <v>0.1853</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1499</v>
+        <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.147</v>
+        <v>0.7271</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0396</v>
+        <v>0.4859</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1075</v>
+        <v>0.2412</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5177</v>
+        <v>0.3139</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5177</v>
+        <v>0.9428</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4911</v>
+        <v>4.9282</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2173</v>
+        <v>1.6297</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2739</v>
+        <v>3.2985</v>
       </c>
       <c r="G4" t="n">
         <v>2.7837</v>
@@ -766,13 +766,13 @@
         <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8546</v>
+        <v>0.2916</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.2133</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0537</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3661</v>
+        <v>4.2622</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8152</v>
+        <v>0.4897</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5509</v>
+        <v>3.7725</v>
       </c>
       <c r="G5" t="n">
         <v>3.0644</v>
@@ -844,13 +844,13 @@
         <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0047</v>
+        <v>-0.0992</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4303</v>
+        <v>0.1048</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4256</v>
+        <v>-0.204</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1929</v>
+        <v>4.1804</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2014</v>
+        <v>1.7457</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9915</v>
+        <v>2.4347</v>
       </c>
       <c r="G6" t="n">
         <v>2.3921</v>
@@ -922,13 +922,13 @@
         <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3846</v>
+        <v>-0.397</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6143</v>
+        <v>-0.0699</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7703</v>
+        <v>-0.3271</v>
       </c>
       <c r="V6" t="n">
         <v>1.2589</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5143</v>
+        <v>2.5909</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0787</v>
+        <v>-1.5344</v>
       </c>
       <c r="F7" t="n">
-        <v>4.593</v>
+        <v>4.1252</v>
       </c>
       <c r="G7" t="n">
         <v>2.1856</v>
@@ -1000,13 +1000,13 @@
         <v>2.2234</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2726</v>
+        <v>0.3491</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5596</v>
+        <v>-0.0152</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8321</v>
+        <v>0.3643</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3144</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1873</v>
+        <v>1.9267</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3127</v>
+        <v>-1.7479</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5</v>
+        <v>3.6747</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0506</v>
+        <v>3.8613</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3224</v>
+        <v>0.2287</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2718</v>
+        <v>3.6326</v>
       </c>
       <c r="J8" t="n">
-        <v>0.904</v>
+        <v>2.4536</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0438</v>
+        <v>-0.1805</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1398</v>
+        <v>2.6341</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1466</v>
+        <v>1.4077</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2786</v>
+        <v>0.4092</v>
       </c>
       <c r="O8" t="n">
-        <v>0.868</v>
+        <v>0.9986</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8529</v>
+        <v>2.2234</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0811</v>
+        <v>-0.4517</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2661</v>
+        <v>-0.4952</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.0435</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9444</v>
+        <v>-0.0005</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.63</v>
+        <v>-0.0005</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.983</v>
+        <v>1.3639</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.347</v>
+        <v>-1.693</v>
       </c>
       <c r="F9" t="n">
-        <v>3.33</v>
+        <v>3.0568</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8613</v>
+        <v>2.0506</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2287</v>
+        <v>2.3224</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6326</v>
+        <v>-0.2718</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4536</v>
+        <v>0.904</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1805</v>
+        <v>2.0438</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6341</v>
+        <v>-1.1398</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4077</v>
+        <v>1.1466</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4092</v>
+        <v>0.2786</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9986</v>
+        <v>0.868</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2234</v>
+        <v>1.8529</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3955</v>
+        <v>0.2577</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0943</v>
+        <v>-0.1141</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3012</v>
+        <v>0.3718</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0005</v>
+        <v>-0.9444</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0005</v>
+        <v>-0.63</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5594</v>
+        <v>-1.9647</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5292</v>
+        <v>-3.1807</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9697</v>
+        <v>1.2159</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2464</v>
@@ -1234,13 +1234,13 @@
         <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9811</v>
+        <v>-0.3864</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5596</v>
+        <v>-0.2111</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4216</v>
+        <v>-0.1754</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6289</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3763</v>
+        <v>-4.9293</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1105</v>
+        <v>-3.762</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2658</v>
+        <v>-1.1673</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4636</v>
@@ -1312,13 +1312,13 @@
         <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8396</v>
+        <v>-0.3926</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7113</v>
+        <v>-0.3628</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1283</v>
+        <v>-0.0299</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8877</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>24.0088</v>
+        <v>24.8295</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.035</v>
+        <v>-4.2145</v>
       </c>
       <c r="F12" t="n">
-        <v>29.0438</v>
+        <v>29.0439</v>
       </c>
       <c r="G12" t="n">
         <v>19.3793</v>
@@ -1390,13 +1390,13 @@
         <v>19.4551</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2435</v>
+        <v>-0.4229000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.573</v>
+        <v>-0.7522</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3291999999999999</v>
+        <v>0.3291</v>
       </c>
       <c r="V12" t="n">
         <v>0.3146000000000002</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.715</v>
+        <v>0.3531</v>
       </c>
       <c r="E13" t="n">
         <v>-1.3421</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0571</v>
+        <v>1.6952</v>
       </c>
       <c r="G13" t="n">
         <v>-2.798</v>
@@ -1468,13 +1468,13 @@
         <v>2.4087</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0694</v>
+        <v>0.7076</v>
       </c>
       <c r="T13" t="n">
         <v>0.0896</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9799</v>
+        <v>0.618</v>
       </c>
       <c r="V13" t="n">
         <v>1.8877</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.0359</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.051</v>
+        <v>-0.3448</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1365</v>
+        <v>0.3088</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0601</v>
@@ -1624,13 +1624,13 @@
         <v>0.7411</v>
       </c>
       <c r="S15" t="n">
-        <v>0.09</v>
+        <v>-0.0314</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1816</v>
+        <v>-0.1122</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0915</v>
+        <v>0.0808</v>
       </c>
       <c r="V15" t="n">
         <v>0.3144</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9428</v>
+        <v>-0.4686</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.622</v>
+        <v>-0.4261</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3208</v>
+        <v>-0.0425</v>
       </c>
       <c r="G16" t="n">
         <v>0.4185</v>
@@ -1702,13 +1702,13 @@
         <v>0.3706</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4909</v>
+        <v>-0.0168</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3283</v>
+        <v>-0.1324</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1627</v>
+        <v>0.1156</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3144</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2612</v>
+        <v>-0.9583</v>
       </c>
       <c r="E17" t="n">
         <v>-0.8988</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3624</v>
+        <v>-0.0594</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7562</v>
@@ -1780,13 +1780,13 @@
         <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3017</v>
+        <v>0.0012</v>
       </c>
       <c r="T17" t="n">
         <v>0.051</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3527</v>
+        <v>-0.0497</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9444</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.301</v>
+        <v>-0.9895</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9889</v>
+        <v>-1.1848</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3121</v>
+        <v>0.1952</v>
       </c>
       <c r="G18" t="n">
         <v>-0.222</v>
@@ -1858,13 +1858,13 @@
         <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>0.291</v>
+        <v>0.6025</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4514</v>
+        <v>0.2556</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1604</v>
+        <v>0.3469</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6289</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>J. CARO SERRANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4976</v>
+        <v>-1.6798</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.3295</v>
+        <v>-1.4197</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8319</v>
+        <v>-0.2601</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.4513</v>
+        <v>-1.148</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.1951</v>
+        <v>-0.1219</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2562</v>
+        <v>-1.0261</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.5882</v>
+        <v>-1.2643</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.1013</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.487</v>
+        <v>-1.2643</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8631</v>
+        <v>0.1163</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0938</v>
+        <v>-0.1219</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2307</v>
+        <v>0.2381</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6676</v>
+        <v>0.1853</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.594</v>
+        <v>0.1853</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9717</v>
+        <v>-0.0883</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1293</v>
+        <v>-0.1554</v>
       </c>
       <c r="U19" t="n">
-        <v>1.101</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3144</v>
+        <v>-0.6289</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CARO SERRANO</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3327</v>
+        <v>-1.9082</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8114</v>
+        <v>-4.4274</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5213</v>
+        <v>2.5193</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.148</v>
+        <v>-4.4513</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1219</v>
+        <v>-4.1951</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0261</v>
+        <v>-0.2562</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2643</v>
+        <v>-3.5882</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-3.1013</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2643</v>
+        <v>-0.487</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1163</v>
+        <v>-0.8631</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1219</v>
+        <v>-1.0938</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2381</v>
+        <v>0.2307</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1853</v>
+        <v>2.594</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7411</v>
+        <v>0.5611</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5471</v>
+        <v>-0.2272</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.194</v>
+        <v>0.7884</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6289</v>
+        <v>0.3144</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6434</v>
+        <v>-4.1101</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8446</v>
+        <v>-5.0404</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2012</v>
+        <v>0.9304</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9972</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9647</v>
+        <v>0.498</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3084</v>
+        <v>0.1126</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6563</v>
+        <v>0.3855</v>
       </c>
       <c r="V21" t="n">
         <v>0.3155</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7354</v>
+        <v>-4.7429</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6777</v>
+        <v>-6.0694</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9423</v>
+        <v>1.3265</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0331</v>
@@ -2170,13 +2170,13 @@
         <v>2.0382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5036</v>
+        <v>0.4962</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6666</v>
+        <v>0.2749</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1629</v>
+        <v>0.2213</v>
       </c>
       <c r="V22" t="n">
         <v>0.3144</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.417199999999999</v>
+        <v>-8.4849</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.8001</v>
+        <v>-8.2125</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6171</v>
+        <v>-0.2724</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6538</v>
@@ -2248,13 +2248,13 @@
         <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1132</v>
+        <v>-0.1809</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0732</v>
+        <v>-0.4856</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0401</v>
+        <v>0.3046</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9444</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-24.0087</v>
+        <v>-22.703</v>
       </c>
       <c r="E24" t="n">
-        <v>-29.044</v>
+        <v>-29.0439</v>
       </c>
       <c r="F24" t="n">
-        <v>5.035300000000001</v>
+        <v>6.341</v>
       </c>
       <c r="G24" t="n">
         <v>-19.3791</v>
@@ -2326,13 +2326,13 @@
         <v>13.8965</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2435</v>
+        <v>2.5492</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3292999999999999</v>
+        <v>-0.3291000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5729</v>
+        <v>2.8785</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3146000000000002</v>
